--- a/design/tables/Theme.xlsx
+++ b/design/tables/Theme.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theme" sheetId="1" r:id="R33e30104c34c45bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theme" sheetId="1" r:id="R5485c2dfc9fd458f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -463,25 +463,25 @@
         <x:v>theme.courtyard.name</x:v>
       </x:c>
       <x:c r="D6" s="2" t="str">
-        <x:v>#e0ddc9</x:v>
+        <x:v>#ffffff</x:v>
       </x:c>
       <x:c r="E6" s="2" t="str">
-        <x:v>#f0dfbd</x:v>
+        <x:v>#fff4df</x:v>
       </x:c>
       <x:c r="F6" s="2" t="str">
-        <x:v>#c7bea3</x:v>
+        <x:v>#ba9c88</x:v>
       </x:c>
       <x:c r="G6" s="2" t="str">
-        <x:v>#d0d5bc</x:v>
+        <x:v>#98deaf</x:v>
       </x:c>
       <x:c r="H6" s="2" t="str">
-        <x:v>#a4ae91</x:v>
+        <x:v>#5cab71</x:v>
       </x:c>
       <x:c r="I6" s="2" t="str">
-        <x:v>#e3e5cf</x:v>
+        <x:v>#ecf8df</x:v>
       </x:c>
       <x:c r="J6" s="2" t="str">
-        <x:v>#bec6af</x:v>
+        <x:v>#72c7b5</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
@@ -495,25 +495,25 @@
         <x:v>theme.rain.name</x:v>
       </x:c>
       <x:c r="D7" s="2" t="str">
-        <x:v>#bfd0cd</x:v>
+        <x:v>#e0f0ff</x:v>
       </x:c>
       <x:c r="E7" s="2" t="str">
-        <x:v>#e0ded0</x:v>
+        <x:v>#fff4df</x:v>
       </x:c>
       <x:c r="F7" s="2" t="str">
-        <x:v>#99b2b1</x:v>
+        <x:v>#ba9c88</x:v>
       </x:c>
       <x:c r="G7" s="2" t="str">
-        <x:v>#b4c4ba</x:v>
+        <x:v>#98deaf</x:v>
       </x:c>
       <x:c r="H7" s="2" t="str">
-        <x:v>#829f99</x:v>
+        <x:v>#5cab71</x:v>
       </x:c>
       <x:c r="I7" s="2" t="str">
-        <x:v>#d5dfd6</x:v>
+        <x:v>#ecf8df</x:v>
       </x:c>
       <x:c r="J7" s="2" t="str">
-        <x:v>#93b5ba</x:v>
+        <x:v>#72c7b5</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
@@ -527,28 +527,28 @@
         <x:v>theme.market.name</x:v>
       </x:c>
       <x:c r="D8" s="2" t="str">
-        <x:v>#e6d1b4</x:v>
+        <x:v>#fff5df</x:v>
       </x:c>
       <x:c r="E8" s="2" t="str">
-        <x:v>#f2e2bb</x:v>
+        <x:v>#fff4df</x:v>
       </x:c>
       <x:c r="F8" s="2" t="str">
-        <x:v>#c5a886</x:v>
+        <x:v>#ba9c88</x:v>
       </x:c>
       <x:c r="G8" s="2" t="str">
-        <x:v>#ced0a9</x:v>
+        <x:v>#98deaf</x:v>
       </x:c>
       <x:c r="H8" s="2" t="str">
-        <x:v>#a6a16f</x:v>
+        <x:v>#5cab71</x:v>
       </x:c>
       <x:c r="I8" s="2" t="str">
-        <x:v>#e6ddbc</x:v>
+        <x:v>#ecf8df</x:v>
       </x:c>
       <x:c r="J8" s="2" t="str">
-        <x:v>#c6ad8e</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="15" hidden="0" customHeight="1">
+        <x:v>#72c7b5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="28" hidden="0" customHeight="1">
       <x:c r="A9" s="7" t="n">
         <x:v>4</x:v>
       </x:c>
@@ -559,25 +559,25 @@
         <x:v>theme.midnight.name</x:v>
       </x:c>
       <x:c r="D9" s="2" t="str">
-        <x:v>#bfc6d6</x:v>
+        <x:v>#d5d7ff</x:v>
       </x:c>
       <x:c r="E9" s="2" t="str">
-        <x:v>#e2dfdf</x:v>
+        <x:v>#fff4df</x:v>
       </x:c>
       <x:c r="F9" s="2" t="str">
-        <x:v>#a0a7bd</x:v>
+        <x:v>#ba9c88</x:v>
       </x:c>
       <x:c r="G9" s="2" t="str">
-        <x:v>#b9c7c7</x:v>
+        <x:v>#98deaf</x:v>
       </x:c>
       <x:c r="H9" s="2" t="str">
-        <x:v>#869ba8</x:v>
+        <x:v>#5cab71</x:v>
       </x:c>
       <x:c r="I9" s="2" t="str">
-        <x:v>#d8dce6</x:v>
+        <x:v>#ecf8df</x:v>
       </x:c>
       <x:c r="J9" s="2" t="str">
-        <x:v>#9dabc6</x:v>
+        <x:v>#72c7b5</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
